--- a/output/pdf_financials_xlsx/SQX.xlsx
+++ b/output/pdf_financials_xlsx/SQX.xlsx
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00018</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.016787</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007164</v>
       </c>
     </row>
     <row r="35">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.00018</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.016787</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.007164</v>
       </c>
     </row>
     <row r="37">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.00074</v>
+        <v>0.00056</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016787</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">

--- a/output/pdf_financials_xlsx/SQX.xlsx
+++ b/output/pdf_financials_xlsx/SQX.xlsx
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.114561</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.234844</v>
       </c>
     </row>
     <row r="65">
@@ -1675,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.114561</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.234844</v>
       </c>
     </row>
     <row r="69">
